--- a/Result/profitability/2754.xlsx
+++ b/Result/profitability/2754.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM33"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4621,6 +4621,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1507</v>
+      </c>
+      <c r="D34" t="n">
+        <v>882</v>
+      </c>
+      <c r="E34" t="n">
+        <v>625</v>
+      </c>
+      <c r="F34" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="G34" t="n">
+        <v>85</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5.67%</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>-17</v>
+      </c>
+      <c r="J34" t="n">
+        <v>69</v>
+      </c>
+      <c r="K34" t="n">
+        <v>55</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.68875</v>
+      </c>
+      <c r="N34" t="n">
+        <v>40.87125</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="X34" t="n">
+        <v>-0.176056338028169</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.7700000000000031</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0.01890962671905716</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.2699999999999999</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.2999999999999998</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.5200000000000031</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.01269221381498675</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK34" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
